--- a/VerveStacks_UZB_grids_kan15/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_UZB_grids_kan15/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_UZB_grids_kan15\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E394A66C-EC1E-481F-A96D-36D9A8FEF4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD807EA4-E4FB-4A12-8B2C-733672B08140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -588,13 +588,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S3aH2,S1aH2,S2aH2</t>
+    <t>S1aH2,S2aH2,S4aH2,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S3aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3</t>
+    <t>S2aH3,S1aH3,S3aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1075,14 +1075,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0ACD839-B60C-4CDA-B632-BF39C559A5EF}">
   <dimension ref="A10:N33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="9.46484375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
         <v>182</v>
@@ -1103,7 +1103,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
         <v>184</v>
@@ -1112,7 +1112,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="I17" s="2">
         <v>0.75</v>
       </c>
@@ -1120,19 +1120,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="3:14" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C18" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="21" spans="3:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="3:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="3:14" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H21" s="3" t="str">
         <f>IF(H23=H24,"Not Required!","~UC_T: LO")</f>
         <v>~UC_T: LO</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="3:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="4" t="s">
         <v>2</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>11</v>
       </c>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S3aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3</v>
+        <v>S2aH3,S1aH3,S3aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1196,7 +1196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
         <v>12</v>
       </c>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S3aH2,S1aH2,S2aH2</v>
+        <v>S1aH2,S2aH2,S4aH2,S3aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1222,12 +1222,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="3:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="29" spans="3:14" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I29" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="3:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="3:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C30" s="4" t="s">
         <v>2</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>26</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H32" t="s">
         <v>31</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
         <v>32</v>
       </c>
@@ -1319,17 +1319,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C86555-E115-49C5-AD6D-547A75F24A6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DD10F7-9393-4F45-901E-D133CD57599A}">
   <dimension ref="A9:G14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C9" t="str">
         <f>IF(A11="x","DeActivated","~TimeSlices")</f>
         <v>~TimeSlices</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>38</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>42</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>44</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>46</v>
       </c>
@@ -1399,11 +1399,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42567AED-6EEC-450C-94E4-20919B3BA49F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B297999-788D-4906-AC6D-DD17DF54D4D1}">
   <dimension ref="B9:J322"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
         <v>~TFM_DINS-AT</v>
@@ -1413,7 +1413,7 @@
         <v>~TFM_DINS-AT</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>48</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>52</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>52</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>52</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>52</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>52</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>52</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>52</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>52</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>52</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>52</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>52</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>52</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>66</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>66</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>66</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>66</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>66</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>66</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>66</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>66</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>66</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>66</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>66</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>66</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>67</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>67</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>67</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>67</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>67</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>67</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>67</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>67</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>67</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>67</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>67</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>67</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>68</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>68</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>68</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>68</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>68</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>68</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>68</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>68</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>68</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>68</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>68</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>68</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>69</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>69</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>69</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>69</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>69</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>69</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>69</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>69</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>69</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>69</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>69</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>69</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>70</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>70</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>70</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>70</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>70</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>70</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>70</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>70</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>70</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>70</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>70</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>70</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>71</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>71</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>71</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>71</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>71</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>71</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>71</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>71</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>71</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>71</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>71</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>71</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>72</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>72</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>72</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>72</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>72</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>72</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>72</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>72</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>72</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>72</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>72</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>72</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>73</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>73</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>73</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>73</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>73</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>73</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>73</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>73</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>73</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>73</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>73</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>73</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>74</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>74</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>74</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>74</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>74</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>74</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>74</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>74</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>74</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>74</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>74</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>74</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>75</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>75</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>75</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>75</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>75</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>75</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>75</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>75</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>75</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>75</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>75</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>75</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>76</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>76</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
         <v>76</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
         <v>76</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
         <v>76</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
         <v>76</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
         <v>76</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>76</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>76</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
         <v>76</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
         <v>76</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
         <v>76</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
         <v>77</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
         <v>77</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
         <v>77</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
         <v>77</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
         <v>77</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
         <v>77</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
         <v>77</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
         <v>77</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
         <v>77</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
         <v>77</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
         <v>77</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
         <v>77</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
         <v>78</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
         <v>78</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
         <v>78</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
         <v>78</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
         <v>78</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
         <v>78</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
         <v>78</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>78</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
         <v>78</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
         <v>78</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>78</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
         <v>78</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>79</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
         <v>79</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
         <v>79</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
         <v>79</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>79</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
         <v>79</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
         <v>79</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
         <v>79</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
         <v>79</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
         <v>79</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>79</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
         <v>79</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
         <v>80</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
         <v>80</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
         <v>80</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
         <v>80</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
         <v>80</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
         <v>80</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
         <v>80</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
         <v>80</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
         <v>80</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
         <v>80</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
         <v>80</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
         <v>80</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
         <v>81</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
         <v>81</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
         <v>81</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
         <v>81</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>81</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
         <v>81</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
         <v>81</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
         <v>81</v>
       </c>
@@ -6639,7 +6639,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
         <v>81</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
         <v>81</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
         <v>81</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
         <v>81</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
         <v>82</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
         <v>82</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
         <v>82</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
         <v>82</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
         <v>82</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
         <v>82</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
         <v>82</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
         <v>82</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
         <v>82</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
         <v>82</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
         <v>82</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
         <v>82</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
         <v>83</v>
       </c>
@@ -7081,7 +7081,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
         <v>83</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
         <v>83</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
         <v>83</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
         <v>83</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
         <v>83</v>
       </c>
@@ -7211,7 +7211,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
         <v>83</v>
       </c>
@@ -7237,7 +7237,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
         <v>83</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
         <v>83</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
         <v>83</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
         <v>83</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
         <v>83</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>84</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
         <v>84</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
         <v>84</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
         <v>84</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
         <v>84</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
         <v>84</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
         <v>84</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
         <v>84</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="247" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
         <v>84</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
         <v>84</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
         <v>84</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
         <v>84</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
         <v>85</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="252" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
         <v>85</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="253" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
         <v>85</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="254" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
         <v>85</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="255" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
         <v>85</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="256" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B256" t="s">
         <v>85</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="257" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
         <v>85</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="258" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
         <v>85</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="259" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
         <v>85</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="260" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
         <v>85</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
         <v>85</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
         <v>85</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="263" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
         <v>86</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="264" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
         <v>86</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="265" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
         <v>86</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
         <v>86</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
         <v>86</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
         <v>86</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="269" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
         <v>86</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="270" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
         <v>86</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
         <v>86</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="272" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
         <v>86</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="273" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
         <v>86</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="274" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
         <v>86</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
         <v>87</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="276" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
         <v>87</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="277" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
         <v>87</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="278" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
         <v>87</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="279" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
         <v>87</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="280" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
         <v>87</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="281" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
         <v>87</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="282" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
         <v>87</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="283" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
         <v>87</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="284" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="284" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
         <v>87</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="285" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="285" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
         <v>87</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="286" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="286" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
         <v>87</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="287" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="287" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
         <v>88</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="288" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
         <v>88</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
         <v>88</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
         <v>88</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
         <v>88</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
         <v>88</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
         <v>88</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
         <v>88</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
         <v>88</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
         <v>88</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
         <v>88</v>
       </c>
@@ -8769,7 +8769,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
         <v>88</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
         <v>89</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
         <v>89</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
         <v>89</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
         <v>89</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
         <v>89</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
         <v>89</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
         <v>89</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
         <v>89</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
         <v>89</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
         <v>89</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
         <v>89</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
         <v>89</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B311" t="s">
         <v>90</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
         <v>90</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B313" t="s">
         <v>90</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314" t="s">
         <v>90</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315" t="s">
         <v>90</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316" t="s">
         <v>90</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317" t="s">
         <v>90</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318" t="s">
         <v>90</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319" t="s">
         <v>90</v>
       </c>
@@ -9077,7 +9077,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B320" t="s">
         <v>90</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B321" t="s">
         <v>90</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B322" t="s">
         <v>90</v>
       </c>
@@ -9125,11 +9125,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A10647-3B92-4CA4-8572-8D69EEB0E43B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{266C206A-41E6-4C86-B00F-A10A82C465BD}">
   <dimension ref="B9:CI59"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-TSL: attribute=FLO_EMIS; other_indexes=ACT")</f>
         <v>~TFM_DINS-TSL: attribute=FLO_EMIS; other_indexes=ACT</v>
@@ -9159,7 +9159,7 @@
         <v>~TFM_DINS-AT</v>
       </c>
     </row>
-    <row r="10" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>51</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>114</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>0.47486438324525732</v>
       </c>
     </row>
-    <row r="12" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>115</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>0.46782432466076473</v>
       </c>
     </row>
-    <row r="13" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>116</v>
       </c>
@@ -10085,7 +10085,7 @@
         <v>0.44316331250975166</v>
       </c>
     </row>
-    <row r="14" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>117</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>0.48067011370645163</v>
       </c>
     </row>
-    <row r="15" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>118</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>0.4756543815608385</v>
       </c>
     </row>
-    <row r="16" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>119</v>
       </c>
@@ -10748,7 +10748,7 @@
         <v>0.45404703652091744</v>
       </c>
     </row>
-    <row r="17" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>120</v>
       </c>
@@ -10969,7 +10969,7 @@
         <v>0.45512011444497352</v>
       </c>
     </row>
-    <row r="18" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>121</v>
       </c>
@@ -11190,7 +11190,7 @@
         <v>0.45400246040168468</v>
       </c>
     </row>
-    <row r="19" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>122</v>
       </c>
@@ -11411,7 +11411,7 @@
         <v>0.46276106832286956</v>
       </c>
     </row>
-    <row r="20" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>123</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>0.46103096489805023</v>
       </c>
     </row>
-    <row r="21" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>124</v>
       </c>
@@ -11853,7 +11853,7 @@
         <v>0.46302134318995231</v>
       </c>
     </row>
-    <row r="22" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>125</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>0.46809455855532339</v>
       </c>
     </row>
-    <row r="23" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>126</v>
       </c>
@@ -12295,7 +12295,7 @@
         <v>0.46570014366255325</v>
       </c>
     </row>
-    <row r="24" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>127</v>
       </c>
@@ -12516,7 +12516,7 @@
         <v>0.47251264797163745</v>
       </c>
     </row>
-    <row r="25" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>128</v>
       </c>
@@ -12737,7 +12737,7 @@
         <v>0.47219177663921824</v>
       </c>
     </row>
-    <row r="26" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>129</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>0.46185190382810631</v>
       </c>
     </row>
-    <row r="27" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>130</v>
       </c>
@@ -13179,7 +13179,7 @@
         <v>0.46895421298183598</v>
       </c>
     </row>
-    <row r="28" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>131</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>0.47909172964517588</v>
       </c>
     </row>
-    <row r="29" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>132</v>
       </c>
@@ -13621,7 +13621,7 @@
         <v>0.48764806584942527</v>
       </c>
     </row>
-    <row r="30" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>133</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>0.48453672290808147</v>
       </c>
     </row>
-    <row r="31" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>134</v>
       </c>
@@ -14063,7 +14063,7 @@
         <v>0.48257764215087751</v>
       </c>
     </row>
-    <row r="32" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>135</v>
       </c>
@@ -14284,7 +14284,7 @@
         <v>0.45940270766184488</v>
       </c>
     </row>
-    <row r="33" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>136</v>
       </c>
@@ -14505,7 +14505,7 @@
         <v>0.47010351523799476</v>
       </c>
     </row>
-    <row r="34" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>137</v>
       </c>
@@ -14726,7 +14726,7 @@
         <v>0.46503582883438693</v>
       </c>
     </row>
-    <row r="35" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>138</v>
       </c>
@@ -14947,7 +14947,7 @@
         <v>0.4768907770413458</v>
       </c>
     </row>
-    <row r="36" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>139</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>0.46823205959896075</v>
       </c>
     </row>
-    <row r="37" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>140</v>
       </c>
@@ -15389,7 +15389,7 @@
         <v>0.27639980189313507</v>
       </c>
     </row>
-    <row r="38" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>141</v>
       </c>
@@ -15610,7 +15610,7 @@
         <v>0.36046134668134944</v>
       </c>
     </row>
-    <row r="39" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>142</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>0.4267799060128078</v>
       </c>
     </row>
-    <row r="40" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>143</v>
       </c>
@@ -16052,7 +16052,7 @@
         <v>0.42377828972053599</v>
       </c>
     </row>
-    <row r="41" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>144</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>0.17280445147129381</v>
       </c>
     </row>
-    <row r="42" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>145</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>0.21742196001405656</v>
       </c>
     </row>
-    <row r="43" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>146</v>
       </c>
@@ -16715,7 +16715,7 @@
         <v>0.24625637282809726</v>
       </c>
     </row>
-    <row r="44" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>147</v>
       </c>
@@ -16936,7 +16936,7 @@
         <v>0.36132475996646979</v>
       </c>
     </row>
-    <row r="45" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>148</v>
       </c>
@@ -17157,7 +17157,7 @@
         <v>0.39710348466145445</v>
       </c>
     </row>
-    <row r="46" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>149</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>0.37478086315861447</v>
       </c>
     </row>
-    <row r="47" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>150</v>
       </c>
@@ -17599,7 +17599,7 @@
         <v>0.47516184313796528</v>
       </c>
     </row>
-    <row r="48" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>151</v>
       </c>
@@ -17820,7 +17820,7 @@
         <v>0.46730083332573369</v>
       </c>
     </row>
-    <row r="49" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>152</v>
       </c>
@@ -18041,7 +18041,7 @@
         <v>0.46723360365564798</v>
       </c>
     </row>
-    <row r="50" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>153</v>
       </c>
@@ -18262,7 +18262,7 @@
         <v>0.53042650732962193</v>
       </c>
     </row>
-    <row r="51" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>154</v>
       </c>
@@ -18483,7 +18483,7 @@
         <v>0.52140330348121877</v>
       </c>
     </row>
-    <row r="52" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>155</v>
       </c>
@@ -18704,7 +18704,7 @@
         <v>0.44389766334589037</v>
       </c>
     </row>
-    <row r="53" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>156</v>
       </c>
@@ -18925,7 +18925,7 @@
         <v>0.39326297527900828</v>
       </c>
     </row>
-    <row r="54" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>157</v>
       </c>
@@ -19146,7 +19146,7 @@
         <v>0.40263226452280537</v>
       </c>
     </row>
-    <row r="55" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>158</v>
       </c>
@@ -19367,7 +19367,7 @@
         <v>0.39948753184361196</v>
       </c>
     </row>
-    <row r="56" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>159</v>
       </c>
@@ -19588,7 +19588,7 @@
         <v>0.14855823196762702</v>
       </c>
     </row>
-    <row r="57" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>160</v>
       </c>
@@ -19809,7 +19809,7 @@
         <v>0.17896822958106751</v>
       </c>
     </row>
-    <row r="58" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>161</v>
       </c>
@@ -20030,7 +20030,7 @@
         <v>0.47601861715358046</v>
       </c>
     </row>
-    <row r="59" spans="2:87" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:87" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>162</v>
       </c>
@@ -20257,11 +20257,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A680CE9-6D62-4E40-8E0A-CECF839FFF89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93F7E29-6E41-43EB-AA00-C7CC4CB0C922}">
   <dimension ref="A9:S38"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
         <v>~TFM_DINS-AT</v>
@@ -20279,7 +20279,7 @@
         <v>~TFM_INS-AT</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -20326,7 +20326,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>8.2191780821917804E-2</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>0.24649520620910059</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>0.10273972602739725</v>
       </c>
@@ -20390,7 +20390,7 @@
         <v>0.16854655975499622</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C13">
         <v>6.1643835616438353E-2</v>
       </c>
@@ -20422,7 +20422,7 @@
         <v>9.1351963673179659E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C14">
         <v>8.4018264840182655E-2</v>
       </c>
@@ -20454,7 +20454,7 @@
         <v>0.34743488326448224</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C15">
         <v>0.1050228310502283</v>
       </c>
@@ -20486,7 +20486,7 @@
         <v>0.29160065632427457</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C16">
         <v>6.3013698630136991E-2</v>
       </c>
@@ -20518,7 +20518,7 @@
         <v>0.25417306285662389</v>
       </c>
     </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>8.4018264840182655E-2</v>
       </c>
@@ -20550,7 +20550,7 @@
         <v>0.2870015206881682</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C18">
         <v>0.1050228310502283</v>
       </c>
@@ -20582,7 +20582,7 @@
         <v>0.2465221213563018</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C19">
         <v>6.3013698630136991E-2</v>
       </c>
@@ -20614,7 +20614,7 @@
         <v>0.2745025300763142</v>
       </c>
     </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C20">
         <v>8.3105022831050229E-2</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>0.35336036041013763</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>0.10388127853881278</v>
       </c>
@@ -20678,7 +20678,7 @@
         <v>0.2268834625622036</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C22">
         <v>6.2328767123287672E-2</v>
       </c>
@@ -20710,7 +20710,7 @@
         <v>0.20420290293386367</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H23" t="s">
         <v>187</v>
       </c>
@@ -20721,7 +20721,7 @@
         <v>8.116392245619318E-2</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
         <v>187</v>
       </c>
@@ -20732,7 +20732,7 @@
         <v>0.10328816085070329</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H25" t="s">
         <v>187</v>
       </c>
@@ -20743,7 +20743,7 @@
         <v>6.247295970663265E-2</v>
       </c>
     </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H26" t="s">
         <v>187</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>8.2765810312001142E-2</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H27" t="s">
         <v>187</v>
       </c>
@@ -20765,7 +20765,7 @@
         <v>0.10544695574605063</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
         <v>187</v>
       </c>
@@ -20776,7 +20776,7 @@
         <v>6.3608573871328414E-2</v>
       </c>
     </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H29" t="s">
         <v>187</v>
       </c>
@@ -20787,7 +20787,7 @@
         <v>8.2355285921566171E-2</v>
       </c>
     </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H30" t="s">
         <v>187</v>
       </c>
@@ -20798,7 +20798,7 @@
         <v>0.10614647400850144</v>
       </c>
     </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H31" t="s">
         <v>187</v>
       </c>
@@ -20809,7 +20809,7 @@
         <v>6.3565968806980219E-2</v>
       </c>
     </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:14" x14ac:dyDescent="0.25">
       <c r="H32" t="s">
         <v>187</v>
       </c>
@@ -20820,7 +20820,7 @@
         <v>8.1839753019258193E-2</v>
       </c>
     </row>
-    <row r="33" spans="8:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
         <v>187</v>
       </c>
@@ -20831,7 +20831,7 @@
         <v>0.10438044678472964</v>
       </c>
     </row>
-    <row r="34" spans="8:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H34" t="s">
         <v>187</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>6.2965688516055135E-2</v>
       </c>
     </row>
-    <row r="35" spans="8:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H35" t="s">
         <v>188</v>
       </c>
@@ -20853,7 +20853,7 @@
         <v>0.60733999999999999</v>
       </c>
     </row>
-    <row r="36" spans="8:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H36" t="s">
         <v>188</v>
       </c>
@@ -20864,7 +20864,7 @@
         <v>0.16952100000000001</v>
       </c>
     </row>
-    <row r="37" spans="8:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H37" t="s">
         <v>188</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>7.9710000000000007E-3</v>
       </c>
     </row>
-    <row r="38" spans="8:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H38" t="s">
         <v>188</v>
       </c>
